--- a/output/full_scan/batch_seq7_2026-10-07.xlsx
+++ b/output/full_scan/batch_seq7_2026-10-07.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1113.604469895617</v>
+        <v>1253.604469895617</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>278.5</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.77205532801102</v>
+        <v>70.77205531460874</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>43.52725427292922</v>
+        <v>43.52725418985412</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>3.460446989561655</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.186809915960107</v>
+        <v>1.186809916850267</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1031.654022632114</v>
+        <v>1201.654022632114</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>273</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>69.47883646925581</v>
+        <v>69.4788364579002</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>32.63783015729784</v>
+        <v>32.63783014858403</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.558480111239997</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.182357922028239</v>
+        <v>1.182357922473343</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6538</v>
+        <v>6715</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>844.653055362549</v>
+        <v>1052.965470639164</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>332</v>
+        <v>485</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,29 +658,29 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>50.70789028211558</v>
+        <v>66.38293819774083</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45.98415798126633</v>
+        <v>27.01424917893566</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>3.772090519424922</v>
+        <v>1.374333551129038</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-15.06491915447194</v>
+        <v>6.766189547398689</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>844</v>
+        <v>1044</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>153.5</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>76.88411643400599</v>
+        <v>76.88411645598153</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>32.88623245730162</v>
+        <v>32.88623253512529</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5.772316451117578</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>3.285850054698088</v>
+        <v>3.285850054475532</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6491</v>
+        <v>6517</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>840.8741691124793</v>
+        <v>974.1553147455244</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>411.5</v>
+        <v>68.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>58.16957995941032</v>
+        <v>59.13207812256121</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>29.6226321998603</v>
+        <v>13.51607166126233</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.632597090118153</v>
+        <v>2.430960800604697</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.3946739782538238</v>
+        <v>0.538460801744703</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6517</v>
+        <v>6485</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>834.1553147455245</v>
+        <v>969.0503124431652</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>68.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>59.13207809684078</v>
+        <v>70.32443215444925</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>13.51607159622201</v>
+        <v>36.52414647668407</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.430960800604697</v>
+        <v>1.994051020726611</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.5384608019227388</v>
+        <v>1.844970507186352</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6485</v>
+        <v>6491</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>799.0503124431652</v>
+        <v>945.8741691124796</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>85.59999999999999</v>
+        <v>411.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>70.32443216114089</v>
+        <v>58.16957994055732</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>36.52414647361041</v>
+        <v>29.62263218694612</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.994051020726611</v>
+        <v>1.632597090118153</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.844970507164098</v>
+        <v>-0.3946739773637038</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6504</v>
+        <v>6834</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>779.6033053894353</v>
+        <v>936.5929523068708</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>37.95</v>
+        <v>125</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.06234648723218</v>
+        <v>63.26563480207481</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>28.45887662474944</v>
+        <v>41.80432447884537</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.789059229803265</v>
+        <v>2.367568613359007</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1089936334684953</v>
+        <v>1.512945877759453</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6715</v>
+        <v>6505</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>767.9654706391639</v>
+        <v>916.7870002110766</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>485</v>
+        <v>107</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.38293819524044</v>
+        <v>76.129308896222</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>27.01424923693653</v>
+        <v>56.97418558168043</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.374333551129038</v>
+        <v>1.205009264110622</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>6.766189547621252</v>
+        <v>1.411705902611082</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6706</v>
+        <v>6658</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>765.8342795324647</v>
+        <v>897.7629123207465</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>154</v>
+        <v>202.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>59.63804051802086</v>
+        <v>72.8131583819317</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>51.29207383428146</v>
+        <v>29.24904782072356</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.57544938614286</v>
+        <v>2.376291232074647</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.2791308120116174</v>
+        <v>2.89586558711005</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6532</v>
+        <v>6504</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>759.066383844652</v>
+        <v>889.6033053894351</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>116.5</v>
+        <v>37.95</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>66.2378127829795</v>
+        <v>56.06234637615925</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45.38936759262167</v>
+        <v>28.45887669001262</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.198857428530531</v>
+        <v>2.789059229803265</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.084444647753834</v>
+        <v>0.1089936334907532</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6834</v>
+        <v>6691</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>736.5929523068708</v>
+        <v>849.6346416401113</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>125</v>
+        <v>776</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>63.26563480159773</v>
+        <v>70.56401205301597</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>41.80432453601905</v>
+        <v>32.30195601079058</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.367568613359007</v>
+        <v>0.7634641640111322</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.512945877759453</v>
+        <v>18.40216948637261</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6768</v>
+        <v>6538</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>731.3000736550853</v>
+        <v>844.653055362549</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>332</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.1888624694092</v>
+        <v>50.70789027792972</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20.96960543178684</v>
+        <v>45.98415796491111</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.723044740414328</v>
+        <v>3.772090519424922</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.4125065169850552</v>
+        <v>-15.06491915429388</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6658</v>
+        <v>6788</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>727.7629123207465</v>
+        <v>844.0489327104791</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>202.5</v>
+        <v>377</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>72.813158376469</v>
+        <v>64.0475221092193</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>29.24904780336128</v>
+        <v>19.68579928357392</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.376291232074647</v>
+        <v>2.506942984646117</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.895865587065536</v>
+        <v>5.405605851345957</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6526</v>
+        <v>6548</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>705.4432348786968</v>
+        <v>825.0401515323331</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>786</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>60.26547991686694</v>
+        <v>60.77347786739208</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>37.9381033776109</v>
+        <v>18.54381491786121</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.49491215050752</v>
+        <v>3.604015153233305</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>5.027239024369791</v>
+        <v>0.6549494551886901</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6788</v>
+        <v>6526</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>704.0489327104785</v>
+        <v>820.4432348786968</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>377</v>
+        <v>786</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>64.04752216953273</v>
+        <v>60.26547990102871</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>19.6857991543386</v>
+        <v>37.93810335127382</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.506942984646117</v>
+        <v>1.49491215050752</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>5.405605850233218</v>
+        <v>5.027239025927614</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6530</v>
+        <v>6742</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>702.2212869709823</v>
+        <v>820.321746866761</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>98.2</v>
+        <v>59.9</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>53.46967738745587</v>
+        <v>70.6671769889806</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>32.19946411361074</v>
+        <v>52.57739255188325</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.312639591466966</v>
+        <v>0.6387816580768609</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.7640144366592274</v>
+        <v>0.7709145694839021</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6742</v>
+        <v>6706</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>690.3217468667609</v>
+        <v>795.834279532465</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>59.9</v>
+        <v>154</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>70.66717697519962</v>
+        <v>59.6380405208971</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>52.5773924818118</v>
+        <v>51.2920738419489</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6387816580768609</v>
+        <v>0.57544938614286</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.7709145691945913</v>
+        <v>-0.2791308119448681</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6664</v>
+        <v>6488</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>686.3791117146505</v>
+        <v>790.3035888626478</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>378</v>
+        <v>1215</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.83680911885104</v>
+        <v>71.92101226047545</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.86335565983988</v>
+        <v>21.47247665201216</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.762307942974693</v>
+        <v>1.130358886264772</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>4.168515116156227</v>
+        <v>33.03651087672175</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6548</v>
+        <v>6525</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>685.0401515323331</v>
+        <v>762.2505809469866</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>77.90000000000001</v>
+        <v>142</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.77347786514288</v>
+        <v>59.82545468585563</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>18.54381491666392</v>
+        <v>14.18870098551053</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.604015153233305</v>
+        <v>1.644945124387673</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.6549494552109364</v>
+        <v>1.630170223678615</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6805</v>
+        <v>6743</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>680.229373092145</v>
+        <v>761.3782102671929</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2455</v>
+        <v>35.75</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.9636981335508</v>
+        <v>88.29600285642994</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>36.03677824461106</v>
+        <v>39.23508371530993</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5837296289857962</v>
+        <v>1.237821026719297</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-11.81182738035018</v>
+        <v>0.6000519957910651</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6525</v>
+        <v>6532</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>647.2505809469866</v>
+        <v>759.066383844652</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>142</v>
+        <v>116.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>59.82545470445589</v>
+        <v>66.23781276154979</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14.18870098152363</v>
+        <v>45.38936758630603</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.644945124387673</v>
+        <v>1.198857428530531</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.630170223322556</v>
+        <v>1.084444647820589</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6505</v>
+        <v>6668</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>631.7870002110766</v>
+        <v>757.6349186333681</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>107</v>
+        <v>50.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>76.12930889081301</v>
+        <v>65.20390702666586</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>56.97418558168044</v>
+        <v>48.96920668894825</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.205009264110622</v>
+        <v>1.136094430571831</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1.411705902611082</v>
+        <v>0.1510747000680035</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6691</v>
+        <v>6768</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>604.6346416401113</v>
+        <v>751.300073655085</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>776</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>70.56401193970089</v>
+        <v>58.18886270734198</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.30195580450018</v>
+        <v>20.96960565923801</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7634641640111322</v>
+        <v>2.723044740414328</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>18.40216949149109</v>
+        <v>0.4125065168737789</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6792</v>
+        <v>6530</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>601.7910239823954</v>
+        <v>702.2212869709823</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>59.8</v>
+        <v>98.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>55.21453968650575</v>
+        <v>53.46967739966851</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>28.64349703307593</v>
+        <v>32.19946405530295</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6251086862012</v>
+        <v>1.312639591466966</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0197211420902179</v>
+        <v>-0.7640144354129852</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6643</v>
+        <v>6789</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>600.6316464569059</v>
+        <v>698.7329704284418</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>498</v>
+        <v>485.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,49 +1877,49 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.73049264322879</v>
+        <v>58.23196037996543</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>34.95079735089996</v>
+        <v>18.36541007017611</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5938300701926819</v>
+        <v>0.6852931900068445</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.792295085678653</v>
+        <v>2.744737214344413</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6668</v>
+        <v>6664</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>597.6349186333681</v>
+        <v>686.3791117146505</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>50.2</v>
+        <v>378</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,49 +1930,49 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>65.20390700888993</v>
+        <v>60.83680902953991</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>48.96920664020847</v>
+        <v>19.86335562411995</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.136094430571831</v>
+        <v>0.762307942974693</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1510747001792776</v>
+        <v>4.168515118492976</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6488</v>
+        <v>6805</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>589.831842563114</v>
+        <v>680.3951842534278</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1215</v>
+        <v>2455</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>71.9210122576077</v>
+        <v>58.96369811038841</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>21.47247656671633</v>
+        <v>36.03677818689892</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.083184256311408</v>
+        <v>0.5973999939322183</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>33.03651087661066</v>
+        <v>-11.81182737478667</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6640</v>
+        <v>6498</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>588.7173307046668</v>
+        <v>622.6611873621493</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1080</v>
+        <v>74.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>48.19024956734521</v>
+        <v>59.56994168356959</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.23173776358369</v>
+        <v>17.68823333225591</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.194970022824753</v>
+        <v>1.673906177809891</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-2.515420200304609</v>
+        <v>1.199646623263601</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6654</v>
+        <v>6531</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>575.6910044477282</v>
+        <v>619.5541555747182</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>217</v>
+        <v>1000</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>59.39317372394447</v>
+        <v>54.58574751363906</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.35801438194565</v>
+        <v>14.78401318505677</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.316088503073954</v>
+        <v>0.9592495525676652</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.8745403387601591</v>
+        <v>5.135134720419714</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6743</v>
+        <v>6792</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>571.378210267193</v>
+        <v>601.7910239823955</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>35.75</v>
+        <v>59.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>88.29600285783816</v>
+        <v>55.21453967739132</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>39.23508359081281</v>
+        <v>28.64349710069891</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.237821026719297</v>
+        <v>0.6251086862012</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.6000519954683781</v>
+        <v>0.019721142134729</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6799</v>
+        <v>6643</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>554.2081000765163</v>
+        <v>600.6316464569059</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>91.5</v>
+        <v>498</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>67.36867648336002</v>
+        <v>56.73049258574736</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.76474640099425</v>
+        <v>34.9507974021473</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4934930261194825</v>
+        <v>0.5938300701926819</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.8961804997559186</v>
+        <v>2.792295086123655</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6642</v>
+        <v>6640</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>536.5629695474831</v>
+        <v>588.717330704667</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>79.09999999999999</v>
+        <v>1080</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>48.48167154751643</v>
+        <v>48.19024954264653</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.21560285188188</v>
+        <v>20.2317377821636</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.493352795526826</v>
+        <v>1.194970022824753</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2276004269815009</v>
+        <v>-2.515420200971872</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6693</v>
+        <v>6654</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>530.947262814616</v>
+        <v>575.6910044477282</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.25463020580342</v>
+        <v>59.39317371599905</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>26.00283606256982</v>
+        <v>28.35801430310649</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.005709093565731</v>
+        <v>2.316088503073954</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,48 +2319,48 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.069550844527775</v>
+        <v>0.8745403389159536</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6806</v>
+        <v>6799</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>554.2081000765163</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>3.51</v>
+        <v>91.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G36" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>31.69634895501747</v>
+        <v>67.36867647419095</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>32.59322849789491</v>
+        <v>32.76474644201193</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.4934930261194825</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.411277083983077</v>
+        <v>0.8961804998671861</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6588</v>
+        <v>6642</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>524.8262568506743</v>
+        <v>536.5629695474831</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>109</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.12283970121565</v>
+        <v>48.48167155628042</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.38863516927676</v>
+        <v>21.21560283867364</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4972968478741957</v>
+        <v>1.493352795526826</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.8271699910954542</v>
+        <v>0.2276004269815009</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6585</v>
+        <v>6693</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>516.208567468148</v>
+        <v>530.947262814616</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.97678777564041</v>
+        <v>52.25463020172776</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>31.50613676899325</v>
+        <v>26.00283602524405</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.961189068981226</v>
+        <v>1.005709093565731</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,48 +2478,48 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.4624521312577307</v>
+        <v>1.069550844550018</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6674</v>
+        <v>6806</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>515.6592428607138</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>18.3</v>
+        <v>3.51</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G39" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>69.57866726976238</v>
+        <v>31.69493958808852</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>38.95051070022854</v>
+        <v>32.59385518904277</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.1503341695200776</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.09419538555560029</v>
+        <v>0.411281829574265</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6782</v>
+        <v>6588</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>504.0441313469152</v>
+        <v>524.8262568506743</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>232.5</v>
+        <v>109</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>50.4888619812636</v>
+        <v>50.12283970121565</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.82230557930732</v>
+        <v>21.38863522750373</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6586202457432321</v>
+        <v>0.4972968478741957</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.81221543211598</v>
+        <v>-0.8271699910287058</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6670</v>
+        <v>6782</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>502.5252243357236</v>
+        <v>524.0441313469153</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>274</v>
+        <v>232.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.96247938123658</v>
+        <v>50.48886197571665</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.67475869800526</v>
+        <v>17.82230560812063</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4709621506080422</v>
+        <v>0.6586202457432321</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.4074362894802302</v>
+        <v>-1.812215431559624</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6789</v>
+        <v>6558</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>493.7329704284422</v>
+        <v>522.6929629180124</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>485.5</v>
+        <v>24.95</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.23196040657429</v>
+        <v>51.37582781213444</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.36541006826333</v>
+        <v>26.30278713038591</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6852931900068445</v>
+        <v>0.6141947607561564</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>2.744737214121946</v>
+        <v>0.173632205784309</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6690</v>
+        <v>6670</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>480.7223855839041</v>
+        <v>522.5252243357235</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>178</v>
+        <v>274</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>56.76519313396275</v>
+        <v>53.96247886765455</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>35.29412225061861</v>
+        <v>18.6747587891774</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.5449305019214929</v>
+        <v>0.4709621506080422</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.6087375904165522</v>
+        <v>-0.4074362873659656</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6589</v>
+        <v>6585</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>474.4865587704662</v>
+        <v>516.208567468148</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>50.6</v>
+        <v>105</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.75209455651054</v>
+        <v>43.97678774656675</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.84965214922989</v>
+        <v>31.50613679748871</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7957774072453753</v>
+        <v>1.961189068981226</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.1143724457863106</v>
+        <v>0.4624521317695764</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6657</v>
+        <v>6674</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>華安</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>468.5575306379229</v>
+        <v>515.6592428607138</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>33.4</v>
+        <v>18.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.12326591872673</v>
+        <v>69.57866714385835</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>21.60537474281451</v>
+        <v>38.95051086558549</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.025907455781923</v>
+        <v>0.1503341695200776</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0419488762439617</v>
+        <v>0.0941953853886921</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6651</v>
+        <v>6776</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>455.6922516216317</v>
+        <v>499.646671099455</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>142.5</v>
+        <v>52.4</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45.25560119601217</v>
+        <v>47.12976805460541</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>18.28353392489589</v>
+        <v>12.26390180818144</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.36773975802217</v>
+        <v>0.7630961075628274</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.3399782759447931</v>
+        <v>0.080308767431521</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6498</v>
+        <v>6690</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>452.6611873621492</v>
+        <v>480.7223855839041</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>74.5</v>
+        <v>178</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.56994153361715</v>
+        <v>56.76519324867839</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.68823330977574</v>
+        <v>35.29412225061861</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.673906177809891</v>
+        <v>0.5449305019214929</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.199646624042509</v>
+        <v>-0.6087375900827414</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6770</v>
+        <v>6589</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>452.3549652280645</v>
+        <v>474.4865587704662</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>50.6</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.79149461817428</v>
+        <v>50.75209444568887</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.25235522497563</v>
+        <v>20.84965217578408</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7833899365829855</v>
+        <v>0.7957774072453753</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0430764358871542</v>
+        <v>-0.1143724456305315</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6689</v>
+        <v>6657</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>華安</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>445.5876845715344</v>
+        <v>468.5575306379228</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>62.7</v>
+        <v>33.4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>46.07155597471663</v>
+        <v>53.123265786662</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.61247401904632</v>
+        <v>21.60537487191443</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.1850662543251879</v>
+        <v>1.025907455781923</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.3816323887481555</v>
+        <v>-0.0419488759546569</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6531</v>
+        <v>6689</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>438.7525312529361</v>
+        <v>465.5876845715344</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1000</v>
+        <v>62.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.58574751537979</v>
+        <v>46.07155592838741</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.784013225458</v>
+        <v>23.61247403926866</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7609743898422768</v>
+        <v>0.1850662543251879</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>5.135134721309726</v>
+        <v>-0.3816323889039341</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6830</v>
+        <v>6651</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>437.7722395541686</v>
+        <v>455.6922516216317</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>530</v>
+        <v>142.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.69337065592386</v>
+        <v>45.25560115124752</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>24.42254267157406</v>
+        <v>18.283533897258</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6434747943834846</v>
+        <v>2.36773975802217</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-5.679632389171168</v>
+        <v>-0.3399782754774492</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6753</v>
+        <v>6550</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>434.424483918958</v>
+        <v>446.6941444835697</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>131</v>
+        <v>16.05</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>40.78615353883241</v>
+        <v>69.03968942789008</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>10.20287440729876</v>
+        <v>32.39700312783287</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4290511223241718</v>
+        <v>0.4428075620326391</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0040147658318678</v>
+        <v>0.5677369056000209</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6756</v>
+        <v>6830</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>433.1120020722996</v>
+        <v>437.7722395541686</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>530</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.10217469541358</v>
+        <v>49.69337062924125</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>14.13364440048644</v>
+        <v>24.42254267499213</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.7632374598853627</v>
+        <v>0.6434747943834846</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0522446445026844</v>
+        <v>-5.679632388280996</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6510</v>
+        <v>6753</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>428.524459270903</v>
+        <v>434.424483918958</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3020</v>
+        <v>131</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.14407631003084</v>
+        <v>40.78615352195565</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>20.89056076254124</v>
+        <v>10.20287435065359</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4089402936409909</v>
+        <v>0.4290511223241718</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-61.72950611802843</v>
+        <v>0.0040147657206044</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6695</v>
+        <v>6756</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>424.5080923874755</v>
+        <v>433.1120020722996</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>51.4</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.08712876093549</v>
+        <v>50.10217468117064</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>23.75258939030867</v>
+        <v>14.13364439440961</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7500058913047406</v>
+        <v>0.7632374598853627</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.2491936870894514</v>
+        <v>0.0522446450145381</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6683</v>
+        <v>6770</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>424.3708767301246</v>
+        <v>432.3549652280645</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1445</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.50290899378729</v>
+        <v>50.79149460825078</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.86066384368102</v>
+        <v>13.25235516249633</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8811465134565561</v>
+        <v>0.7833899365829855</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-18.302150707303</v>
+        <v>0.0430764359539126</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6831</v>
+        <v>6510</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>417.8057599409497</v>
+        <v>428.5244592709029</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>488</v>
+        <v>3020</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>38.15134960690562</v>
+        <v>44.14407627811872</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>24.26949393533518</v>
+        <v>20.89056076550661</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6681346501301049</v>
+        <v>0.4089402936409909</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.9816784493421622</v>
+        <v>-61.72950609755488</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6739</v>
+        <v>6669</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>413.5576624809544</v>
+        <v>426.8563687721555</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1100</v>
+        <v>2240</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.99805418647868</v>
+        <v>32.04679702300979</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11.06882857099395</v>
+        <v>44.8442402150048</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3067049821254033</v>
+        <v>0.9867524625511142</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-3.711374773930285</v>
+        <v>143.6831253636911</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6558</v>
+        <v>6683</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>412.6929629180255</v>
+        <v>424.3708767301246</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>24.95</v>
+        <v>1445</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.37582740277959</v>
+        <v>49.50290897371107</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>26.30278715753822</v>
+        <v>17.86066381342326</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6141947607561564</v>
+        <v>0.8811465134565561</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.1736322058065623</v>
+        <v>-18.3021507036309</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6561</v>
+        <v>6641</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>409.851441152513</v>
+        <v>423.5254752313114</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>313</v>
+        <v>17.15</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.1834116971499</v>
+        <v>51.69077830103181</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>20.56277983085779</v>
+        <v>7.998045149463948</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.9837352335110816</v>
+        <v>0.6883457920497088</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.5181155264444945</v>
+        <v>0.1697734425643115</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6763</v>
+        <v>6831</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>409.4847168292525</v>
+        <v>417.8057599409497</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>41.5</v>
+        <v>488</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.30418472847415</v>
+        <v>38.15134947832595</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.93075574551483</v>
+        <v>24.26949401926911</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.139716421409076</v>
+        <v>0.6681346501301049</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0576307675200723</v>
+        <v>0.9816784541268966</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6606</v>
+        <v>6695</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>408.1789666973122</v>
+        <v>414.5080923874755</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>24.25</v>
+        <v>51.4</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>39.25201806573059</v>
+        <v>52.08712867659366</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>30.02151679420391</v>
+        <v>23.75258936105657</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.275510750672252</v>
+        <v>0.7500058913047406</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0845068677729405</v>
+        <v>0.2491936872229774</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6684</v>
+        <v>6739</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>405.8003867861256</v>
+        <v>413.5576624809545</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>48.45</v>
+        <v>1100</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>50.93121894924801</v>
+        <v>48.99805417669018</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>27.1927655469664</v>
+        <v>11.06882857832127</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8535192842313095</v>
+        <v>0.3067049821254033</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0782248786567004</v>
+        <v>-3.711374773596463</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6556</v>
+        <v>6561</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>398.4511607309822</v>
+        <v>409.851441152513</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>62.3</v>
+        <v>313</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>55.93330618034834</v>
+        <v>46.18341165212075</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8.219273874877945</v>
+        <v>20.5627799198944</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.25848347820654</v>
+        <v>0.9837352335110816</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1411294153448209</v>
+        <v>0.5181155270008748</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6584</v>
+        <v>6763</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>395.8558438379639</v>
+        <v>409.4847168292444</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>538</v>
+        <v>41.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>43.22144341461435</v>
+        <v>51.30418463775465</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>17.8776029042149</v>
+        <v>16.93075577194153</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.655911272491956</v>
+        <v>1.139716421409076</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.8232988765081046</v>
+        <v>0.0576307674755655</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6722</v>
+        <v>6606</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>392.5320962560044</v>
+        <v>408.1789666973121</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>33</v>
+        <v>24.25</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>54.38269587470388</v>
+        <v>39.25201806573059</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.5115011938302</v>
+        <v>30.02151676382989</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.101032128403935</v>
+        <v>1.275510750672252</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.08437204891855909</v>
+        <v>-0.0845068677618146</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6771</v>
+        <v>6684</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>372.7954746133037</v>
+        <v>405.800386786127</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>42.3</v>
+        <v>48.45</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.45354371168843</v>
+        <v>50.93121884078155</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>19.7393396995441</v>
+        <v>27.19276551793284</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.3540802925346998</v>
+        <v>0.8535192842313095</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0364501210524829</v>
+        <v>0.0782248787902188</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6732</v>
+        <v>6556</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>371.8820669379746</v>
+        <v>398.4511607309821</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>153</v>
+        <v>62.3</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.89340580877934</v>
+        <v>55.9333061051049</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>18.26427010729456</v>
+        <v>8.219273857750933</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.8123895642229532</v>
+        <v>1.25848347820654</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.9501429186017976</v>
+        <v>0.1411294155006064</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6579</v>
+        <v>6584</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>367.8901138433915</v>
+        <v>395.8558438379639</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>153</v>
+        <v>538</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>48.51093797435255</v>
+        <v>43.22144343584493</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>14.82506630789203</v>
+        <v>17.87760284387238</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.305961479714457</v>
+        <v>1.655911272491956</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.5468113704621882</v>
+        <v>-0.8232988772870407</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6560</v>
+        <v>6722</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>363.8320521718499</v>
+        <v>392.5320962560044</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>33.05</v>
+        <v>33</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.5636283324406</v>
+        <v>54.38269607290106</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12.02753035478657</v>
+        <v>22.51150130566764</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>3.718428319850982</v>
+        <v>2.101032128403935</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.0021903724251642</v>
+        <v>0.08437204891855909</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6781</v>
+        <v>6821</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>361.8924373711101</v>
+        <v>384.0021447496327</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>1025</v>
+        <v>45.55</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>47.55921984717945</v>
+        <v>62.70353582016127</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.38958346005812</v>
+        <v>25.89823952722393</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.8960641202813358</v>
+        <v>1.204040616338487</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,11 +4227,11 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>3.966518758097363</v>
+        <v>0.6955293035139316</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>361.6269426853838</v>
+        <v>381.6269426853833</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>94</v>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>62.73689028423542</v>
+        <v>62.73689027393267</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.06401835770535</v>
+        <v>19.06401833803405</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>1.304920841320401</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4290,21 +4290,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6577</v>
+        <v>6771</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>361.433609974081</v>
+        <v>372.7954746133037</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>80.5</v>
+        <v>42.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.31879980235127</v>
+        <v>54.45354366514866</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.25618224630758</v>
+        <v>19.73933982704787</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3530786296324553</v>
+        <v>0.3540802925346998</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1713994914847433</v>
+        <v>-0.0364501210302321</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6725</v>
+        <v>6732</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>347.8337725241277</v>
+        <v>371.8820669379746</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>43.72824629073453</v>
+        <v>53.89340584478774</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>17.47254200042025</v>
+        <v>18.26427008500916</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7243381253323696</v>
+        <v>0.8123895642229532</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.761486618607498</v>
+        <v>0.9501429186017976</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6591</v>
+        <v>6579</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>342.4885870323934</v>
+        <v>367.8901138433915</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>42.25</v>
+        <v>153</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.17325392915908</v>
+        <v>48.51093799902613</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>28.43353553492006</v>
+        <v>14.82506629531328</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.7450420307279888</v>
+        <v>2.305961479714457</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0698294408020607</v>
+        <v>0.5468113702396373</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6692</v>
+        <v>6560</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>337.2260941198513</v>
+        <v>363.8320521718499</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>22.6</v>
+        <v>33.05</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.92579482110285</v>
+        <v>52.5636283817698</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7.06733949261104</v>
+        <v>12.0275304727065</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.424990315444385</v>
+        <v>3.718428319850982</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.1129516051866721</v>
+        <v>-0.0021903726588295</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6835</v>
+        <v>6781</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>337.1061833502353</v>
+        <v>361.8924373711102</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>32.05</v>
+        <v>1025</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>60.3999276890191</v>
+        <v>47.55922003504973</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>18.95237335428656</v>
+        <v>10.38958345946432</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.030699029542193</v>
+        <v>0.8960641202813358</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1554238964067159</v>
+        <v>3.966518746970348</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6550</v>
+        <v>6577</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>336.6941444835697</v>
+        <v>361.433609974081</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>16.05</v>
+        <v>80.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>69.03968954910808</v>
+        <v>53.31879974351804</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>32.39700311969303</v>
+        <v>12.25618223808673</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4428075620326391</v>
+        <v>0.3530786296324553</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.5677369055293906</v>
+        <v>0.1713994915515075</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6655</v>
+        <v>6796</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>335.1716001157791</v>
+        <v>358.377800861895</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>128.5</v>
+        <v>56</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>52.42859627811433</v>
+        <v>53.7621408255878</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11.54198484134593</v>
+        <v>22.58410100179937</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.1171600115779159</v>
+        <v>0.4111745347817654</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>3.000680723797135</v>
+        <v>0.8150799613422983</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6645</v>
+        <v>6541</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>331.7560237395261</v>
+        <v>358.0455968885669</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>12.3</v>
+        <v>32.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>40.56365506034467</v>
+        <v>52.17129661921657</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>24.10606632951998</v>
+        <v>21.40567213082549</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>2.080335114416762</v>
+        <v>1.384758286420315</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0270251361641453</v>
+        <v>0.4511644762330913</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6776</v>
+        <v>6835</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>314.6466710994553</v>
+        <v>357.1061833502348</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>52.4</v>
+        <v>32.05</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.12976827960137</v>
+        <v>60.39992763303238</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>12.26390178437936</v>
+        <v>18.95237335565402</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.7630961075628274</v>
+        <v>1.030699029542193</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0803087673870124</v>
+        <v>0.1554238965068623</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6512</v>
+        <v>6552</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>314.257270417908</v>
+        <v>352.3127723681343</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>20.2</v>
+        <v>24.6</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.9591509153349</v>
+        <v>50.40322449515867</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>8.696316584827279</v>
+        <v>17.68958511987298</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4685132996504769</v>
+        <v>1.140799689730528</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.6251091005357816</v>
+        <v>0.1040280828485496</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6761</v>
+        <v>6725</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>314.0625764318856</v>
+        <v>347.8337725241277</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>168.5</v>
+        <v>217</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.42581210194743</v>
+        <v>43.72824647360349</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>14.20791959599376</v>
+        <v>17.47254193633597</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.4025229968208498</v>
+        <v>0.7243381253323696</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.6499457094196077</v>
+        <v>1.761486615825714</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6641</v>
+        <v>6591</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>313.5254752313114</v>
+        <v>342.4885870324041</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>17.15</v>
+        <v>42.25</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>51.69077831660468</v>
+        <v>43.17325358788264</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>7.998045049034449</v>
+        <v>28.43353563499133</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6883457920497088</v>
+        <v>0.7450420307279888</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1697734425531838</v>
+        <v>-0.0698294404014799</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6477</v>
+        <v>6692</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>309.2108752351925</v>
+        <v>337.2260941198513</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>33.85</v>
+        <v>22.6</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45.11374462390012</v>
+        <v>49.92579483738111</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.8022473657366</v>
+        <v>7.067339593196125</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3046942904262522</v>
+        <v>1.424990315444385</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0075768219674523</v>
+        <v>0.1129516050753999</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6666</v>
+        <v>6655</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>309.1400236863805</v>
+        <v>335.1716001157791</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>44.05</v>
+        <v>128.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.70383803661524</v>
+        <v>52.4285962800246</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.38444204555786</v>
+        <v>11.54198484660188</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.319279439184921</v>
+        <v>0.1171600115779159</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0920360655923239</v>
+        <v>3.000680723685861</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6605</v>
+        <v>6645</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>308.8934381424509</v>
+        <v>331.756023739526</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>137.5</v>
+        <v>12.3</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.35420993970324</v>
+        <v>40.56365485808269</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>11.66111143425054</v>
+        <v>24.10606629829069</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.6461663422583031</v>
+        <v>2.080335114416762</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2357111234638984</v>
+        <v>0.0270251361975265</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6829</v>
+        <v>6719</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>306.7204331151829</v>
+        <v>318.2709753403984</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>215</v>
+        <v>189.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.30686013655792</v>
+        <v>50.25926005145746</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10.67132842969841</v>
+        <v>16.64660363714146</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.055740541579798</v>
+        <v>0.5572014010305308</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.6871527515900002</v>
+        <v>1.790596203385054</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6515</v>
+        <v>6512</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>303.5569304895243</v>
+        <v>314.257270417908</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>5520</v>
+        <v>20.2</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>38.54218235185567</v>
+        <v>51.9591509153349</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.49449842880621</v>
+        <v>8.696316582402833</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>3.047409186114112</v>
+        <v>0.4685132996504769</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-21.24033232681805</v>
+        <v>-0.625109100591416</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6494</v>
+        <v>6761</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>299.0686910091588</v>
+        <v>314.0625764318856</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>52.1</v>
+        <v>168.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>48.89617476928266</v>
+        <v>49.42581231150218</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11.12763401053118</v>
+        <v>14.20791960037839</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7835738852996059</v>
+        <v>0.4025229968208498</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>2</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.2814004694369266</v>
+        <v>0.6499457096421595</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6719</v>
+        <v>6477</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>298.2709753403984</v>
+        <v>309.2108752351925</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>189.5</v>
+        <v>33.85</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>50.25926009591462</v>
+        <v>45.11374466370713</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.64660363124644</v>
+        <v>18.80224731324377</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5572014010305308</v>
+        <v>0.3046942904262522</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.790596203385054</v>
+        <v>-0.007576822023086</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6568</v>
+        <v>6666</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>288.486252798228</v>
+        <v>309.1400236863805</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>139.5</v>
+        <v>44.05</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>51.58789048525239</v>
+        <v>42.70383788421154</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>17.48529050118664</v>
+        <v>12.38444204555787</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7344733591900754</v>
+        <v>1.319279439184921</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1415752827083993</v>
+        <v>-0.09203606531414781</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6598</v>
+        <v>6605</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>288.2520528098219</v>
+        <v>308.8934381424509</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>26.75</v>
+        <v>137.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.82327249830934</v>
+        <v>50.35420982868564</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.46215453984397</v>
+        <v>11.66111145590354</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7719791554012105</v>
+        <v>0.6461663422583031</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1045979459554937</v>
+        <v>-0.2357111235751973</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6669</v>
+        <v>6829</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>285.5054167720663</v>
+        <v>306.7204331151829</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>2240</v>
+        <v>215</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>32.04679704127558</v>
+        <v>49.30686010533363</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>44.84424026288349</v>
+        <v>10.67132841580111</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7858898632306404</v>
+        <v>1.055740541579798</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>143.6831253614657</v>
+        <v>-0.6871527521463494</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6486</v>
+        <v>6494</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>270.9901711701982</v>
+        <v>299.0686910091596</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>52.1</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>43.14673343954686</v>
+        <v>48.89617477327645</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>39.16518609624641</v>
+        <v>11.12763405661541</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4044651309561375</v>
+        <v>0.7835738852996059</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.4980440351552376</v>
+        <v>0.2814004694035395</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6794</v>
+        <v>6515</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>向榮生技-創</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>266.3012383636357</v>
+        <v>288.5569304895247</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>72</v>
+        <v>5520</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>42.83664049641421</v>
+        <v>38.54218231931112</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.24994014259486</v>
+        <v>11.49449840865958</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.330800469676686</v>
+        <v>3.047409186114112</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.1435771887394421</v>
+        <v>-21.24033230233979</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6581</v>
+        <v>6568</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>264.4647546794623</v>
+        <v>288.486252798228</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>108</v>
+        <v>139.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>44.63405688201458</v>
+        <v>51.58789046203457</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>13.85682894479422</v>
+        <v>17.48529050986868</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.769079634063977</v>
+        <v>0.7344733591900754</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1270470916107983</v>
+        <v>-0.1415752825971339</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6735</v>
+        <v>6598</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>261.7958355407471</v>
+        <v>288.2520528098219</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>63.2</v>
+        <v>26.75</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.25472234554317</v>
+        <v>43.82327249131359</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>23.15736118120049</v>
+        <v>12.46215455721599</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.475972184562545</v>
+        <v>0.7719791554012105</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.3239368547190217</v>
+        <v>-0.1045979459443668</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6741</v>
+        <v>6794</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>向榮生技-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>249.4820394575434</v>
+        <v>286.3012383636357</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>54.2</v>
+        <v>72</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>31.79771730849661</v>
+        <v>42.83664047565681</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>28.1248457535331</v>
+        <v>16.24994014899622</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6099438016528925</v>
+        <v>1.330800469676686</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.3830515315775815</v>
+        <v>-0.1435771886504245</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6671</v>
+        <v>6581</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>246.486134079298</v>
+        <v>284.4647546794625</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>23.05</v>
+        <v>108</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>51.56681851306146</v>
+        <v>44.63405665418254</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>17.36777207490593</v>
+        <v>13.85682876554633</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.9635784293953938</v>
+        <v>2.769079634063977</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0379678661272595</v>
+        <v>-0.1270470912769729</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6821</v>
+        <v>6486</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>244.0021447496316</v>
+        <v>270.9901711701982</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>45.55</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>62.70353583461584</v>
+        <v>43.14673337682815</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>25.89823946550397</v>
+        <v>39.16518606616907</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.204040616338487</v>
+        <v>0.4044651309561375</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.6955293034026596</v>
+        <v>-0.4980440350217077</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6796</v>
+        <v>6671</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>243.3778008618951</v>
+        <v>266.4861340792979</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>56</v>
+        <v>23.05</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>53.76214080536726</v>
+        <v>51.56681847522093</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>22.5841009690727</v>
+        <v>17.36777207490593</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4111745347817654</v>
+        <v>0.9635784293953938</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.8150799612977917</v>
+        <v>0.0379678660827565</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6541</v>
+        <v>6735</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>243.0455968885668</v>
+        <v>261.7958355407472</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>32.7</v>
+        <v>63.2</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>52.17129675815795</v>
+        <v>46.25472233560773</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>21.40567182020312</v>
+        <v>23.15736118257492</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.384758286420315</v>
+        <v>1.475972184562545</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.4511644757212463</v>
+        <v>0.3239368547523952</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6552</v>
+        <v>6741</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>242.3127723681343</v>
+        <v>249.4820394575434</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>24.6</v>
+        <v>54.2</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.4032244403375</v>
+        <v>31.79771761897067</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>17.68958520883582</v>
+        <v>28.12484568477366</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.140799689730528</v>
+        <v>0.6099438016528925</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,11 +5976,11 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1040280828596774</v>
+        <v>-0.383051532067182</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>46.71665187007897</v>
+        <v>46.7166515045681</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.59589348863984</v>
+        <v>22.59589359598293</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>0.7189753876545146</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.2164948078428034</v>
+        <v>0.2164948088887581</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>46.74867707805699</v>
+        <v>46.74867695683746</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>20.82770975250212</v>
+        <v>20.82770974453937</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>1.087118739762186</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0544406832079821</v>
+        <v>0.0544406831857218</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>43.26920209373665</v>
+        <v>43.26920226335194</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>17.49615689856017</v>
+        <v>17.49615691271331</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.7055216616004415</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0440192961903501</v>
+        <v>0.0440192961836712</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>34.10909094914619</v>
+        <v>34.10909095053115</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.96959038620508</v>
+        <v>12.96959035136759</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-1.363933958950013</v>
+        <v>-1.36393395901677</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.62527951946826</v>
+        <v>41.6252794317053</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>16.95370135519132</v>
+        <v>16.95370148066986</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>0.5270466302598856</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0082723224049009</v>
+        <v>-0.0082723222936262</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.14534877563816</v>
+        <v>44.1453487645686</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>12.50176140834709</v>
+        <v>12.50176142364174</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.6165052564730895</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.7042061760239429</v>
+        <v>0.7042061764690257</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>41.10716203604553</v>
+        <v>41.10716200413965</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.34457999609712</v>
+        <v>19.34457993171669</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.5449254690436086</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2401337160350753</v>
+        <v>0.2401337160795864</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>214.25770112009</v>
+        <v>214.2577011200901</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>262</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>25.77921589005496</v>
+        <v>25.77921600477022</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>24.01427113455655</v>
+        <v>24.01427114249524</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>1.35336230736192</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.3938904512722949</v>
+        <v>-0.393890451383609</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6421,7 +6421,7 @@
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>213.9857891583089</v>
+        <v>213.9857891583101</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>31.9</v>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.86051126760943</v>
+        <v>48.86051142973943</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.26624660561976</v>
+        <v>12.26624663203817</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>1.494401109881914</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0098484669294978</v>
+        <v>0.009848466795974301</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>206.7142120300498</v>
+        <v>206.7142120300499</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>31.3</v>
@@ -6491,7 +6491,7 @@
         <v>47.03911133117432</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>11.66022614526505</v>
+        <v>11.66022613259007</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>1.025741069686733</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0494492464077624</v>
+        <v>0.0494492464745265</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>183.6920466011757</v>
+        <v>183.6920466011761</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>56.6</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>34.22964250741964</v>
+        <v>34.22964229443792</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>34.45468875700018</v>
+        <v>34.45468898002476</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.7146699755841779</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.2126948500327936</v>
+        <v>-0.2126948497657415</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>181.1538564798034</v>
+        <v>181.1538564798033</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>64.8</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.76715421988919</v>
+        <v>51.76715422037367</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>7.103708529764799</v>
+        <v>7.103708550042394</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>0.1281613339912197</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-1.764790468739923</v>
+        <v>-1.764790468450619</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>51.79927338372687</v>
+        <v>51.79927337980487</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>6.85881112152949</v>
+        <v>6.85881111199693</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.7712243397340856</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>1.471140989004302</v>
+        <v>1.471140989160087</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>51.57708378147577</v>
+        <v>51.57708376091636</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>4.863238661745258</v>
+        <v>4.863238716713616</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>1.498025330246493</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.0579646245446614</v>
+        <v>0.0579646248339653</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>34.5883163726967</v>
+        <v>34.58831634451302</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.77528080233857</v>
+        <v>19.77528088679697</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>1.360843100568703</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0350156482564678</v>
+        <v>-0.0350156482342166</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6546</v>
+        <v>6625</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>138.401089046158</v>
+        <v>138.9568420890008</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>61.5</v>
+        <v>73.8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>54.77016682900375</v>
+        <v>41.35151134035616</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.82949674275573</v>
+        <v>13.66727120966688</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.6595153603578683</v>
+        <v>0.3806931468109763</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>1</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.3306732897085777</v>
+        <v>0.035034079027634</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6720</v>
+        <v>6546</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>126.3992371656878</v>
+        <v>138.401089046158</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>124.5</v>
+        <v>61.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>49.00680801774007</v>
+        <v>54.77016665411341</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>13.33804452527546</v>
+        <v>14.82949671841813</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.2551928319780022</v>
+        <v>0.6595153603578683</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.5573647963357709</v>
+        <v>0.3306732899533809</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6754</v>
+        <v>6720</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>105.430638449121</v>
+        <v>126.3992371656875</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>40.5</v>
+        <v>124.5</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>39.57875052524912</v>
+        <v>49.00680805888578</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>13.21668825250289</v>
+        <v>13.33804459166437</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.443063844912104</v>
+        <v>0.2551928319780022</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.0715508236370707</v>
+        <v>0.5573647956681522</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>6625</v>
+        <v>6754</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>必應</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>63.95684208900283</v>
+        <v>105.430638449121</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>73.8</v>
+        <v>40.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>41.35151156312786</v>
+        <v>39.57875053049892</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.66727125654261</v>
+        <v>13.21668823175602</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3806931468109763</v>
+        <v>1.443063844912104</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0350340794727289</v>
+        <v>-0.07155082368157351</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
